--- a/output/Tables/Modal shift/disease_modal_shift_100replicate.xlsx
+++ b/output/Tables/Modal shift/disease_modal_shift_100replicate.xlsx
@@ -444,22 +444,22 @@
         </is>
       </c>
       <c r="D2">
-        <v>2459230.606</v>
+        <v>2483216.965</v>
       </c>
       <c r="E2">
-        <v>2276375.023</v>
+        <v>2297368.698</v>
       </c>
       <c r="F2">
-        <v>2706499.977</v>
+        <v>2734533.24</v>
       </c>
       <c r="G2">
-        <v>25981301.409</v>
+        <v>26225669.906</v>
       </c>
       <c r="H2">
-        <v>24692695.716</v>
+        <v>24927274.997</v>
       </c>
       <c r="I2">
-        <v>27384976.575</v>
+        <v>27640008.443</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -471,13 +471,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>3460509.453</v>
+        <v>3493048.42</v>
       </c>
       <c r="N2">
-        <v>3259860.361</v>
+        <v>3290875.046</v>
       </c>
       <c r="O2">
-        <v>3621290.151</v>
+        <v>3655050.528</v>
       </c>
     </row>
     <row r="3">
@@ -489,44 +489,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="D3">
-        <v>1445082.762</v>
+        <v>1009622.86</v>
       </c>
       <c r="E3">
-        <v>1344857.908</v>
+        <v>957597.701</v>
       </c>
       <c r="F3">
-        <v>1545372.745</v>
+        <v>1061681.826</v>
       </c>
       <c r="G3">
-        <v>1266057.618</v>
+        <v>1518222.56</v>
       </c>
       <c r="H3">
-        <v>1195769.405</v>
+        <v>1418987.611</v>
       </c>
       <c r="I3">
-        <v>1351627.244</v>
+        <v>1639032.252</v>
       </c>
       <c r="J3">
-        <v>80550.913</v>
+        <v>14957.339</v>
       </c>
       <c r="K3">
-        <v>75420.412</v>
+        <v>14249.403</v>
       </c>
       <c r="L3">
-        <v>86733.24099999999</v>
+        <v>15810.412</v>
       </c>
       <c r="M3">
-        <v>168233.947</v>
+        <v>201709.403</v>
       </c>
       <c r="N3">
-        <v>158435.238</v>
+        <v>187875.301</v>
       </c>
       <c r="O3">
-        <v>177126.425</v>
+        <v>214264.063</v>
       </c>
     </row>
     <row r="4">
@@ -538,44 +538,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="D4">
-        <v>1011114.885</v>
+        <v>1471670.261</v>
       </c>
       <c r="E4">
-        <v>957891.059</v>
+        <v>1367362.584</v>
       </c>
       <c r="F4">
-        <v>1053476.735</v>
+        <v>1554690.714</v>
       </c>
       <c r="G4">
-        <v>1540062.793</v>
+        <v>1281564.537</v>
       </c>
       <c r="H4">
-        <v>1429655.036</v>
+        <v>1202802.197</v>
       </c>
       <c r="I4">
-        <v>1640909.567</v>
+        <v>1353506.293</v>
       </c>
       <c r="J4">
-        <v>14936.573</v>
+        <v>81716.90399999999</v>
       </c>
       <c r="K4">
-        <v>14140.321</v>
+        <v>75846.54399999999</v>
       </c>
       <c r="L4">
-        <v>15672.58</v>
+        <v>87143.101</v>
       </c>
       <c r="M4">
-        <v>203899.605</v>
+        <v>169785.537</v>
       </c>
       <c r="N4">
-        <v>189996.566</v>
+        <v>159867.431</v>
       </c>
       <c r="O4">
-        <v>215725.978</v>
+        <v>178222.198</v>
       </c>
     </row>
     <row r="5">
@@ -591,40 +591,40 @@
         </is>
       </c>
       <c r="D5">
-        <v>202177.022</v>
+        <v>182626.874</v>
       </c>
       <c r="E5">
-        <v>190095.293</v>
+        <v>171761.789</v>
       </c>
       <c r="F5">
-        <v>213383.934</v>
+        <v>192705.236</v>
       </c>
       <c r="G5">
-        <v>394435.293</v>
+        <v>351343.011</v>
       </c>
       <c r="H5">
-        <v>371445.217</v>
+        <v>331096.425</v>
       </c>
       <c r="I5">
-        <v>418459.115</v>
+        <v>372499.983</v>
       </c>
       <c r="J5">
-        <v>15200.041</v>
+        <v>13730.241</v>
       </c>
       <c r="K5">
-        <v>14201.382</v>
+        <v>12832.147</v>
       </c>
       <c r="L5">
-        <v>15987.883</v>
+        <v>14438.746</v>
       </c>
       <c r="M5">
-        <v>52309.395</v>
+        <v>46596.081</v>
       </c>
       <c r="N5">
-        <v>49314.331</v>
+        <v>43958.429</v>
       </c>
       <c r="O5">
-        <v>56325.553</v>
+        <v>50132.976</v>
       </c>
     </row>
     <row r="6">
@@ -640,40 +640,40 @@
         </is>
       </c>
       <c r="D6">
-        <v>488109.013</v>
+        <v>483420.943</v>
       </c>
       <c r="E6">
-        <v>444007.503</v>
+        <v>439641.886</v>
       </c>
       <c r="F6">
-        <v>545005.401</v>
+        <v>539901.328</v>
       </c>
       <c r="G6">
-        <v>765322.704</v>
+        <v>749454.319</v>
       </c>
       <c r="H6">
-        <v>709183.267</v>
+        <v>694483.748</v>
       </c>
       <c r="I6">
-        <v>822847.3959999999</v>
+        <v>805781.304</v>
       </c>
       <c r="J6">
-        <v>8309.641</v>
+        <v>8230.038</v>
       </c>
       <c r="K6">
-        <v>7431.219</v>
+        <v>7358.038</v>
       </c>
       <c r="L6">
-        <v>9139.837</v>
+        <v>9054.164000000001</v>
       </c>
       <c r="M6">
-        <v>101324.337</v>
+        <v>99223.49400000001</v>
       </c>
       <c r="N6">
-        <v>93629.889</v>
+        <v>91689.25</v>
       </c>
       <c r="O6">
-        <v>107427.293</v>
+        <v>105199.382</v>
       </c>
     </row>
     <row r="7">
@@ -689,22 +689,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>4727623.583</v>
+        <v>4789248.047</v>
       </c>
       <c r="E7">
-        <v>4466596.266</v>
+        <v>4524820.608</v>
       </c>
       <c r="F7">
-        <v>4959877.395</v>
+        <v>5024527.181</v>
       </c>
       <c r="G7">
-        <v>13243808.842</v>
+        <v>14454785.656</v>
       </c>
       <c r="H7">
-        <v>12365579.2</v>
+        <v>13497186.318</v>
       </c>
       <c r="I7">
-        <v>14180466.498</v>
+        <v>15476093.42</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -716,13 +716,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1766467.941</v>
+        <v>1927983.469</v>
       </c>
       <c r="N7">
-        <v>1628293.327</v>
+        <v>1777321.373</v>
       </c>
       <c r="O7">
-        <v>1914903.689</v>
+        <v>2089834.046</v>
       </c>
     </row>
   </sheetData>
